--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Governance Dashboard'!$A$4:$I$68</definedName>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Governance Dashboard'!$A$4:$I$68</definedName>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Enforce `EnabledWithTranscript` via Teams meeting policy for all user groups with recordkeeping obligations — override the change announced September 2025 (MC1139493, effective late April 2026) that changed the global `-Copilot` default from `EnabledWithTranscript` to `Enabled`. FSI firms must explicitly set `-Copilot "EnabledWithTranscript"` on all regulated meeting policies to maintain transcript-coupled Copilot behavior required for record-keeping:</t>
+          <t>Enforce `EnabledWithTranscript` via Teams meeting policy for all user groups with recordkeeping obligations — current Microsoft Learn documentation identifies `EnabledWithTranscript` as the default `-Copilot` value, but FSI firms must explicitly set `-Copilot "EnabledWithTranscript"` on all regulated meeting policies to maintain transcript-coupled Copilot behavior required for recordkeeping:</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Governance Dashboard'!$A$4:$I$68</definedName>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Enforce `EnabledWithTranscript` via Teams meeting policy for all user groups with recordkeeping obligations — override the change announced September 2025 (MC1139493, effective late April 2026) that changed the global `-Copilot` default from `EnabledWithTranscript` to `Enabled`. FSI firms must explicitly set `-Copilot "EnabledWithTranscript"` on all regulated meeting policies to maintain transcript-coupled Copilot behavior required for record-keeping:</t>
+          <t>Enforce `EnabledWithTranscript` via Teams meeting policy for all user groups with recordkeeping obligations — current Microsoft Learn documentation identifies `EnabledWithTranscript` as the default `-Copilot` value, but FSI firms must explicitly set `-Copilot "EnabledWithTranscript"` on all regulated meeting policies to maintain transcript-coupled Copilot behavior required for recordkeeping:</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -2536,7 +2536,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Commission independent FFIEC readiness assessment for Copilot governance, covering all relevant booklets (Information Security, AIO, Audit, Management) and supplemental guidance (OCC Bulletin 2025-26, SR 11-7)</t>
+          <t>Commission independent FFIEC readiness assessment for Copilot governance, covering all relevant booklets (Information Security, AIO, Audit, Management) and supplemental guidance (OCC Bulletin 2026-13 / Federal Reserve SR 26-2 revised Model Risk Management guidance, with OCC Bulletin 2025-26 retained as community-bank proportionality context)</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Configure WORM-immutable retention for records subject to SEC Rule 17a-4(f) requirements — use `New-RetentionComplianceRule` with `-RetentionComplianceAction KeepAndDelete` to support immutable retain-then-delete behavior required for WORM compliance</t>
+          <t>Configure WORM-style immutable retention for records the firm identifies as subject to SEC Rule 17a-4(f) requirements — use `New-RetentionComplianceRule` with `-RetentionComplianceAction KeepAndDelete` to support immutable retain-then-delete behavior; firms should confirm WORM applicability with counsel</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Increase post-use review sampling rate to 25% of Copilot-assisted communications (FSI-recommended baseline); configure via CC policy &gt; Review percentage in the Purview portal</t>
+          <t>Increase post-use review sampling rate to the firm's approved threshold for Copilot-assisted communications (25% is an FSI policy example; confirm with compliance/legal); configure via CC policy &gt; Review percentage in the Purview portal</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Configure WORM-style immutable retention for records the firm identifies as subject to SEC Rule 17a-4(f) requirements — use `New-RetentionComplianceRule` with `-RetentionComplianceAction KeepAndDelete` to support immutable retain-then-delete behavior; firms should confirm WORM applicability with counsel</t>
+          <t>Configure WORM-style immutable retention for records the firm identifies as subject to SEC Rule 17a-4(f) requirements — use `New-RetentionComplianceRule` with `-RetentionComplianceAction KeepAndDelete` to support immutable retain-then-delete behavior; WORM applicability: confirm</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Increase post-use review sampling rate to the firm's approved threshold for Copilot-assisted communications (25% is an FSI policy example; confirm with compliance/legal); configure via CC policy &gt; Review percentage in the Purview portal</t>
+          <t>Increase post-use review sampling rate to the firm's approved threshold for Copilot-assisted communications (default threshold: 25%; adjust to the firm-approved threshold with compliance/legal); configure via CC policy &gt; Review percentage in the Purview portal</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Configure WORM-immutable retention for records subject to SEC Rule 17a-4(f) requirements — use `New-RetentionComplianceRule` with `-RetentionComplianceAction KeepAndDelete` to support immutable retain-then-delete behavior required for WORM compliance</t>
+          <t>Configure WORM-style immutable retention for records the firm identifies as subject to SEC Rule 17a-4(f) requirements — use `New-RetentionComplianceRule` with `-RetentionComplianceAction KeepAndDelete` to support immutable retain-then-delete behavior; WORM applicability: confirm</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Increase post-use review sampling rate to 25% of Copilot-assisted communications (FSI-recommended baseline); configure via CC policy &gt; Review percentage in the Purview portal</t>
+          <t>Increase post-use review sampling rate to the firm's approved threshold for Copilot-assisted communications (default threshold: 25%; adjust to the firm-approved threshold with compliance/legal); configure via CC policy &gt; Review percentage in the Purview portal</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -3198,17 +3198,17 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Document the tenant's Cowork access posture: which users/groups have usage-based billing enabled, whether the discovery setting is on, and the approval basis for both decisions</t>
+          <t>Document the tenant's Cowork access posture: which users/groups are in a spending policy that selects Cowork, whether the discovery setting is on, and the approval basis for both decisions</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Manage usage-based billing scope, discovery, model toggles, browser-use toggle, and consumption limits through a documented change register</t>
+          <t>Manage Cowork spending-policy scope, discovery, model toggles, browser-use toggle, and consumption limits through a documented change register</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Require dual approval (technology + compliance) before enabling usage-based billing, discovery, browser use, or the Anthropic/Fable model toggles for any regulated or client-facing population</t>
+          <t>Require dual approval (technology + compliance) before enabling Cowork spending-policy access, discovery, browser use, or Anthropic/model controls for any regulated or client-facing population</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr"/>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Minimum Chinese Wall implementation — addresses the most critical regulatory separation requirements including the Channel Agent IB limitation</t>
+          <t>Minimum ethical-wall implementation for firms whose approved policy requires segment separation, including explicit handling of the Channel Agent IB limitation</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Full Chinese Wall implementation for large, diversified financial institutions subject to frequent SEC/FINRA examinations. The Channel Agent limitation and compensating controls must appear in the examination package.</t>
+          <t>Full ethical-wall implementation for large, diversified financial institutions subject to frequent examinations. The Channel Agent limitation and compensating controls should appear in the examination package where counsel/compliance determine the cited rules or firm policies apply.</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr"/>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -2694,7 +2694,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Define which user groups have Copilot enabled for Teams Phone via calling policies — Copilot can run during PSTN and 1:1 VoIP calls, and AI-generated call summaries are produced when transcription is captured. The `-Copilot` parameter on `Set-CsTeamsCallingPolicy` controls call-Copilot availability (`Enabled` is the documented default; `EnabledWithTranscript` requires a started transcript before Copilot is offered; `Disabled` turns Copilot off for calls). For FSI recordkeeping, `EnabledWithTranscript` paired with `-AllowTranscriptionForCalling $true` is the recommended baseline so call Copilot only runs when a transcript is captured. Configure via Teams Admin Center &gt; Voice &gt; Calling policies:</t>
+          <t>Define which user groups have Copilot enabled for Teams Phone via calling policies — Copilot can run during PSTN and 1:1 VoIP calls, and after-call access depends on recording or transcription. The `-Copilot` parameter on `Set-CsTeamsCallingPolicy` controls call-Copilot availability (`Enabled` is the documented default; `EnabledWithTranscript` requires a licensed user to start transcription before Copilot is offered; `Disabled` turns Copilot off for calls). For FSI recordkeeping, `EnabledWithTranscript` paired with `-AllowTranscriptionForCalling $true` is the recommended baseline so call Copilot only runs when a transcript is captured. Configure via Teams Admin Center &gt; Voice &gt; Calling policies:</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Implement WORM-compliant storage for Copilot records per SEC Rule 17a-4(f) — either via Option A (audit-trail alternative: Purview regulatory record labels + Preservation Lock with documented compliance analysis per Rule 17a-4(f)(2)), or Option B (third-party WORM archival with vendor attestation)</t>
+          <t>Implement the firm/counsel-approved SEC Rule 17a-4(f) posture for Copilot records — either via Option A (Purview regulatory record labels + Preservation Lock + audit evidence as support for the firm's Rule 17a-4(f)(2) assessment), Option B (third-party WORM archival with vendor attestation), or both</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr"/>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Governance Dashboard'!$A$4:$I$68</definedName>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Enable the Microsoft 365 data connector in Sentinel</t>
+          <t>Enable the Microsoft Copilot data connector in Sentinel for `CopilotActivity`</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Governance Dashboard'!$A$4:$I$68</definedName>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Document the tenant's Cowork access posture: which users/groups are in a spending policy that selects Cowork, whether the discovery setting is on, and the approval basis for both decisions</t>
+          <t>Document the tenant's Cowork access posture: which users/groups are in a spending policy that selects Cowork, the state of the current discovery/request setting, and the approval basis for both decisions</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Manage Cowork spending-policy scope, discovery, model toggles, browser-use toggle, and consumption limits through a documented change register</t>
+          <t>Manage Cowork spending-policy scope, the current discovery/request setting, model toggles, browser-use toggle, and consumption limits through a documented change register</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Governance Dashboard'!$A$4:$I$68</definedName>
@@ -1602,17 +1602,17 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Provides visibility into Copilot usage patterns without impacting user experience — essential first step for understanding AI interaction behavior. Agent monitoring alerts provide baseline coverage for agent-involved incidents.</t>
+          <t>Provides initial visibility without assuming unsupported native-client coverage or prompt-level telemetry. Shadow AI review and agent monitoring extend the control beyond first-party Copilot alone.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Active monitoring with real-time alerting — suitable for production FSI Copilot deployments where proactive threat detection is needed. Generative AI catalog and agent anomaly detection extend coverage to Shadow AI and agentic threats.</t>
+          <t>Active monitoring with supported browser-session controls and Shadow AI governance, while reserving Purview audit for Copilot prompt/response evidence.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Full session-level governance with automated response — designed for firms with the highest security monitoring requirements. Agent threat detection and Shadow AI governance satisfy FINRA supervisory obligations for agentic AI.</t>
+          <t>Full session-level governance with stronger enforcement on supported browser surfaces, explicit native-client compensating controls, and documented Shadow AI/agent governance evidence.</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
@@ -1644,17 +1644,17 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Provides foundational insider risk detection and agent monitoring — minimum monitoring for Copilot deployment in regulated environments</t>
+          <t>Provides foundational insider risk detection and agent monitoring without assuming that optional Security Copilot agent features are already licensed or approved</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Comprehensive insider risk program incorporating AI-specific indicators and agent governance — suitable for most FSI firms</t>
+          <t>Comprehensive insider risk program incorporating AI-specific indicators, optional triage automation, and agent governance — suitable for most FSI firms</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Full insider risk governance with continuous improvement and agent supervisory coverage — designed for firms with active insider threat programs and board-level risk oversight</t>
+          <t>Full insider risk governance with continuous improvement, explicit preview-feature governance, and board-ready evidence for firms with active insider threat programs</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr"/>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -3198,12 +3198,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Document the tenant's Cowork access posture: which users/groups are in a spending policy that selects Cowork, whether the discovery setting is on, and the approval basis for both decisions</t>
+          <t>Document the tenant's Cowork access posture: which users/groups are in a spending policy that selects Cowork, the state of the current discovery/request setting, and the approval basis for both decisions</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Manage Cowork spending-policy scope, discovery, model toggles, browser-use toggle, and consumption limits through a documented change register</t>
+          <t>Manage Cowork spending-policy scope, the current discovery/request setting, model toggles, browser-use toggle, and consumption limits through a documented change register</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1602,17 +1602,17 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Provides visibility into Copilot usage patterns without impacting user experience — essential first step for understanding AI interaction behavior. Agent monitoring alerts provide baseline coverage for agent-involved incidents.</t>
+          <t>Provides initial visibility without assuming unsupported native-client coverage or prompt-level telemetry. Shadow AI review and agent monitoring extend the control beyond first-party Copilot alone.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Active monitoring with real-time alerting — suitable for production FSI Copilot deployments where proactive threat detection is needed. Generative AI catalog and agent anomaly detection extend coverage to Shadow AI and agentic threats.</t>
+          <t>Active monitoring with supported browser-session controls and Shadow AI governance, while reserving Purview audit for Copilot prompt/response evidence.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Full session-level governance with automated response — designed for firms with the highest security monitoring requirements. Agent threat detection and Shadow AI governance satisfy FINRA supervisory obligations for agentic AI.</t>
+          <t>Full session-level governance with stronger enforcement on supported browser surfaces, explicit native-client compensating controls, and documented Shadow AI/agent governance evidence.</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
@@ -1644,17 +1644,17 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Provides foundational insider risk detection and agent monitoring — minimum monitoring for Copilot deployment in regulated environments</t>
+          <t>Provides foundational insider risk detection and agent monitoring without assuming that optional Security Copilot agent features are already licensed or approved</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Comprehensive insider risk program incorporating AI-specific indicators and agent governance — suitable for most FSI firms</t>
+          <t>Comprehensive insider risk program incorporating AI-specific indicators, optional triage automation, and agent governance — suitable for most FSI firms</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Full insider risk governance with continuous improvement and agent supervisory coverage — designed for firms with active insider threat programs and board-level risk oversight</t>
+          <t>Full insider risk governance with continuous improvement, explicit preview-feature governance, and board-ready evidence for firms with active insider threat programs</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr"/>

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Maximum restriction during initial Copilot deployment — eliminates third-party extensibility risk entirely</t>
+          <t>Maximum restriction during initial Copilot deployment — helps reduce third-party extensibility risk</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">

--- a/assessment/templates/governance-maturity-dashboard.xlsx
+++ b/assessment/templates/governance-maturity-dashboard.xlsx
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Plugin and Graph Connector Security Governance</t>
+          <t>Plugin and Copilot Connector Security Governance</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Maximum restriction during initial Copilot deployment — eliminates third-party extensibility risk entirely</t>
+          <t>Maximum restriction during initial Copilot deployment — helps reduce third-party extensibility risk</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
